--- a/歌手巡演专辑数据.xlsx
+++ b/歌手巡演专辑数据.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>香港迪士尼乐园幻想岛露天场地</t>
+          <t>香港迪士尼乐园幻想道露天场地</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>天津奥体中心</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>美高梅大酒店</t>
+          <t>米高梅大花园体育馆</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>大连大麦体育文化中心</t>
+          <t>大连体育中心体育馆</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>天津体育中心体育馆</t>
+          <t>天津体育馆</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>东莞体育中心体育馆</t>
+          <t>东莞篮球中心</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>西安城市体育馆</t>
+          <t>西安城市运动公园体育馆</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>康州金神体育馆</t>
+          <t>康涅狄格金神体育馆</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>东京</t>
+          <t>横滨</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>天津体育中心体育馆</t>
+          <t>天津体育馆</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>长沙国际会展中心</t>
+          <t>湖南国际会展中心</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>金神大赌场体育馆</t>
+          <t>康涅狄格金神体育馆</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>休斯顿河口音乐中心</t>
+          <t>休斯顿Bayou音乐中心</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>台北中信金融园区</t>
+          <t>台北南港C3停车场（中信金融园区）</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>香港迪士尼幻想道露天场地</t>
+          <t>香港迪士尼乐园幻想道露天场地</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>天津体育中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>美高梅大花园体育馆</t>
+          <t>米高梅大花园体育馆</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -23231,7 +23231,7 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>天津奥体中心</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
@@ -25087,7 +25087,7 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>天津奥林匹克体育中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -28225,7 +28225,7 @@
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>美高梅大花园体育馆</t>
+          <t>米高梅大花园体育馆</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
@@ -29057,7 +29057,7 @@
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>嘉兴体育中心</t>
+          <t>嘉兴市体育中心体育场</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -29409,7 +29409,7 @@
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>长沙国际会展中心</t>
+          <t>湖南国际会展中心</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
@@ -29985,7 +29985,7 @@
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>金神体育馆</t>
+          <t>康涅狄格金神体育馆</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -30017,7 +30017,7 @@
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>东莞东风日产文体中心</t>
+          <t>东莞篮球中心</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>天津体育中心体育馆</t>
+          <t>天津体育馆</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -31457,7 +31457,7 @@
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>新加坡展览中心</t>
+          <t>新加坡博览中心</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
@@ -32028,12 +32028,12 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>纽约</t>
+          <t>纽瓦克</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>纽约保德信中心</t>
+          <t>保德信中心</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
@@ -32604,12 +32604,12 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>纽约</t>
+          <t>康涅狄格州</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>金神大赌场体育馆</t>
+          <t>康涅狄格金神体育馆</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>米高梅竞技场</t>
+          <t>米高梅大花园体育馆</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -32929,7 +32929,7 @@
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>米高梅竞技场</t>
+          <t>米高梅大花园体育馆</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
@@ -33281,7 +33281,7 @@
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>天津奥林匹克体育中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>天津奥林匹克体育中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">
@@ -35137,7 +35137,7 @@
       </c>
       <c r="D1085" t="inlineStr">
         <is>
-          <t>东莞东风日产文体中心</t>
+          <t>东莞篮球中心</t>
         </is>
       </c>
       <c r="E1085" t="inlineStr">
@@ -37249,7 +37249,7 @@
       </c>
       <c r="D1151" t="inlineStr">
         <is>
-          <t>天津市奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1151" t="inlineStr">
@@ -37473,7 +37473,7 @@
       </c>
       <c r="D1158" t="inlineStr">
         <is>
-          <t>天津奥体中心</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1158" t="inlineStr">
@@ -37793,7 +37793,7 @@
       </c>
       <c r="D1168" t="inlineStr">
         <is>
-          <t>天津奥体中心</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1168" t="inlineStr">
@@ -38689,7 +38689,7 @@
       </c>
       <c r="D1196" t="inlineStr">
         <is>
-          <t>天津奥体中心</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1196" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="D1209" t="inlineStr">
         <is>
-          <t>天津市奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1209" t="inlineStr">
@@ -40481,7 +40481,7 @@
       </c>
       <c r="D1252" t="inlineStr">
         <is>
-          <t>天津奥林匹克中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1252" t="inlineStr">

--- a/歌手巡演专辑数据.xlsx
+++ b/歌手巡演专辑数据.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1298"/>
+  <dimension ref="A1:F1329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.83203125" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>梅赛德斯-奔驰文化中心</t>
+          <t>上海梅赛德斯-奔驰文化中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>长沙贺龙体育中心体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>吉隆坡</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>吉隆坡武吉加里尔国家体育场</t>
+          <t>武吉加里尔国家体育场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>五源河体育场</t>
+          <t>海口五源河体育场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>山西体育中心</t>
+          <t>山西体育中心体育场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>海峡奥体中心</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>贺龙体育中心</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>深圳大运中心</t>
+          <t>深圳大运中心体育场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>南京奥体中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>广西体育中心</t>
+          <t>广西体育中心体育场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>启德体育园主场馆</t>
+          <t>香港启德主场馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>白鹭体育场</t>
+          <t>厦门奥林匹克体育中心-白鹭体育场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>济南奥体中心</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>广西体育中心主体育场</t>
+          <t>广西体育中心体育场</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>南京奥体中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>广州天河体育中心</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>武吉加里尔国家体育场（TM国家体育场）</t>
+          <t>武吉加里尔国家体育场</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市体育中心</t>
+          <t>深圳体育场</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>贵阳奥体中心</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>苏州体育中心体育场</t>
+          <t>苏州市体育中心体育场</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>佛山世纪莲体育中心</t>
+          <t>佛山世纪莲体育中心体育场</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>红磡香港体育馆</t>
+          <t>红磡体育馆</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>悉尼Allphones Arena</t>
+          <t>库多斯银行体育馆</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>长沙贺龙体育中心</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>梅赛德斯-奔驰文化中心</t>
+          <t>上海梅赛德斯-奔驰文化中心</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>福州海峡奥体中心体育场</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>梅赛德斯-奔驰文化中心</t>
+          <t>上海梅赛德斯-奔驰文化中心</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>首都体育馆</t>
+          <t>北京首都体育馆</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>成都市体育中心</t>
+          <t>成都体育中心体育场</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>武汉体育中心体育场</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>布特拉室内体育馆</t>
+          <t>吉隆坡亚通体育馆</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>福建省奥林匹克体育中心</t>
+          <t>福建省体育中心体育场</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>重庆市奥林匹克体育中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>南京奥林匹克体育中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄龙体育中心体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>贵阳市奥林匹克体育中心</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>贺龙体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>合肥奥林匹克体育中心</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>河南省体育中心</t>
+          <t>河南省体育中心体育场</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>山西省体育中心红灯笼体育场</t>
+          <t>山西体育中心体育场</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>天河体育中心体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>布特拉室内体育馆</t>
+          <t>吉隆坡亚通体育馆</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>成都市体育中心</t>
+          <t>成都体育中心体育场</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>重庆市奥林匹克体育中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>南京奥林匹克体育中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>黄龙体育中心体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>济南奥林匹克体育中心体育场</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>厦门市体育中心</t>
+          <t>厦门市体育中心体育场</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>佛山世纪莲体育中心</t>
+          <t>佛山世纪莲体育中心体育场</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>徐州奥林匹克体育中心体育场</t>
+          <t>徐州奥体中心主体育场</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>苏州体育中心体育场</t>
+          <t>苏州市体育中心体育场</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>河南省体育中心</t>
+          <t>河南省体育中心体育场</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>合肥奥林匹克体育中心体育场</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>南京奥林匹克体育中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>武汉沌口体育场</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>成都市体育中心</t>
+          <t>成都体育中心体育场</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>福建省奥林匹克体育中心</t>
+          <t>福建省体育中心体育场</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>重庆市奥林匹克体育中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>黄龙体育中心体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>圣荷西</t>
+          <t>圣何塞</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>圣荷西SAP中心</t>
+          <t>圣何塞SAP中心</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>天河体育中心体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>布特拉室内体育馆</t>
+          <t>吉隆坡亚通体育馆</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>济南奥林匹克体育中心体育场</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>贺龙体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>南通体育会展中心</t>
+          <t>南通体育会展中心体育场</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>苏州体育中心体育场</t>
+          <t>苏州市体育中心体育场</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>新华路体育场</t>
+          <t>武汉新华路体育场</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>黄龙体育中心体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Shrine Auditorium</t>
+          <t>圣殿剧院</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>康州</t>
+          <t>康涅狄格州</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Mohegan Sun Arena</t>
+          <t>康涅狄格金神体育馆</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>苏州体育中心体育场</t>
+          <t>苏州市体育中心体育场</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>哈尔滨国际会展中心体育场</t>
+          <t>哈尔滨国际会展体育中心体育场</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>天河体育中心体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>天河体育中心体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>金光综艺-威尼斯人综合馆</t>
+          <t>澳门威尼斯人金光综艺馆</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>南京奥林匹克体育中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>重庆市奥林匹克体育中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>贺龙体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>贵阳新体育场</t>
+          <t>贵阳市新体育场</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>厦门市体育中心</t>
+          <t>厦门市体育中心体育场</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>武汉沌口体育场</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>成都市体育中心</t>
+          <t>成都体育中心体育场</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>黄龙体育中心体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>拓东体育场</t>
+          <t>昆明拓东体育场</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Air Canada Centre</t>
+          <t>多伦多加拿大航空中心</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>康州</t>
+          <t>康涅狄格州</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Mohegan Sun Arena</t>
+          <t>康涅狄格金神体育馆</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Acer Arena</t>
+          <t>库多斯银行体育馆</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>佛山世纪莲体育中心</t>
+          <t>佛山世纪莲体育中心体育场</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>伊利沙伯女皇剧院</t>
+          <t>伊丽莎白女王剧院</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>天河体育中心体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育馆</t>
+          <t>深圳湾体育中心“春茧”体育馆</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>悉尼库多斯银行体育馆</t>
+          <t>库多斯银行体育馆</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>墨尔本罗德·拉沃竞技场</t>
+          <t>罗德·拉沃竞技场</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>苏州体育中心体育场</t>
+          <t>苏州市体育中心体育场</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>厦门体育中心体育场</t>
+          <t>厦门市体育中心体育场</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>石家庄裕彤体育场</t>
+          <t>石家庄裕彤国际体育中心</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>佛山世纪莲体育中心</t>
+          <t>佛山世纪莲体育中心体育场</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>青岛国信体育场</t>
+          <t>青岛国信体育中心体育场</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>珠海体育中心体育场</t>
+          <t>珠海市体育中心体育场</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>金华体育中心体育场</t>
+          <t>金华市体育中心体育场</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>吉隆坡武吉加里尔国家体育场</t>
+          <t>武吉加里尔国家体育场</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>上海大舞台</t>
+          <t>上海体育馆</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育馆</t>
+          <t>深圳湾体育中心“春茧”体育馆</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>凯撒皇宫酒店罗马大剧场</t>
+          <t>凯撒宫大剧场</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>澳门金光综艺馆</t>
+          <t>澳门威尼斯人金光综艺馆</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>哈尔滨国际会展中心体育馆</t>
+          <t>哈尔滨国际会展体育中心体育馆</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>北京万事达中心</t>
+          <t>北京凯迪拉克中心</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>合肥奥林匹克体育中心体育场</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>济南奥林匹克体育中心东荷体育馆</t>
+          <t>济南奥体中心东荷体育馆</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>太原山西省体育馆</t>
+          <t>山西省体育馆</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>桃园国际棒球场</t>
+          <t>乐天桃园棒球场</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>安卡斯维尔</t>
+          <t>康涅狄格州</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>圣荷西</t>
+          <t>圣何塞</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>圣荷西SAP中心</t>
+          <t>圣何塞SAP中心</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>巴克莱中心</t>
+          <t>纽约巴克莱中心</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>雅高体育馆</t>
+          <t>巴黎雅高体育馆</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>温布利体育馆</t>
+          <t>伦敦温布利体育馆</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场（大莲花）</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>哈尔滨国际会展中心体育场</t>
+          <t>哈尔滨国际会展体育中心体育场</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>兰州奥体中心玫瑰体育场</t>
+          <t>兰州奥体中心体育场</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>郑州奥体中心郑地体育场</t>
+          <t>郑州奥体中心体育场</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>重庆奥体中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Scotiabank Arena</t>
+          <t>多伦多加拿大航空中心</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Chase Center</t>
+          <t>大通中心</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>纽约巴克莱中心</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>The O2</t>
+          <t>伦敦O2体育馆</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Qudos Bank Arena</t>
+          <t>库多斯银行体育馆</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Rod Laver Arena</t>
+          <t>罗德·拉沃竞技场</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>启德体育园主场馆</t>
+          <t>香港启德主场馆</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>圣荷西</t>
+          <t>圣何塞</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>San Jose State University Event Center</t>
+          <t>圣何塞州立大学活动中心</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>红磡香港体育馆</t>
+          <t>红磡体育馆</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>集美嘉庚体育馆</t>
+          <t>厦门嘉庚体育馆</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>天河体育中心体育馆</t>
+          <t>广州天河体育中心体育馆</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>云顶</t>
+          <t>云顶高原</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>云顶高原</t>
+          <t>云顶云星剧场</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>国立台湾体育运动大学 台中校址田径场</t>
+          <t>国立台湾体育运动大学田径场</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Hisense Arena</t>
+          <t>John Cain Arena</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>虹口足球场</t>
+          <t>上海虹口足球场</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>首都体育馆</t>
+          <t>北京首都体育馆</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>黄龙体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>南京奥林匹克体育中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>岭南明珠体育馆</t>
+          <t>佛山岭南明珠体育馆</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>康涅狄格</t>
+          <t>康涅狄格州</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>圣荷西</t>
+          <t>圣何塞</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>San Jose State University Event Center</t>
+          <t>圣何塞州立大学活动中心</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Hisense Arena</t>
+          <t>John Cain Arena</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>武吉贾利勒布特拉室内体育馆</t>
+          <t>吉隆坡亚通体育馆</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>南京五台山体育中心体育场</t>
+          <t>南京五台山体育场</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>广西壮族自治区体育场</t>
+          <t>广西体育场</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>广州天河体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>洛杉矶Memorial Sports Arena</t>
+          <t>洛杉矶纪念体育竞技场</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>吉隆坡布特拉室内体育馆</t>
+          <t>吉隆坡亚通体育馆</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>杭州黄龙体育中心</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>重庆奥林匹克体育中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>常州奥体中心体育场</t>
+          <t>常州奥体中心新城体育场</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>厦门体育中心体育场</t>
+          <t>厦门市体育中心体育场</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>巴黎天顶音乐厅</t>
+          <t>巴黎天顶体育馆</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -16255,12 +16255,12 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>圣荷西</t>
+          <t>圣何塞</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>圣荷西州立活动中心</t>
+          <t>圣何塞州立大学活动中心</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>洛杉矶Memorial Sports Arena</t>
+          <t>洛杉矶纪念体育竞技场</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>广东省奥林匹克体育中心</t>
+          <t>广东奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>东京Zepp Tokyo</t>
+          <t>Zepp Tokyo</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>东京日本武道馆</t>
+          <t>日本武道馆</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>成都体育中心</t>
+          <t>成都体育中心体育场</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>南京奥体中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>吉隆坡默迪卡体育场</t>
+          <t>默迪卡体育场</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>桃园国际棒球场</t>
+          <t>乐天桃园棒球场</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>广州大学城中心体育场</t>
+          <t>广州大学城体育中心体育场</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>厦门体育中心体育场</t>
+          <t>厦门市体育中心体育场</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -17604,7 +17604,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>黄龙体育中心体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>河南省体育中心</t>
+          <t>河南省体育中心体育场</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>济南奥体中心西柳体育场</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>山西体育中心红灯笼体育场</t>
+          <t>山西体育中心体育场</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>贵阳奥体中心</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -17956,7 +17956,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>广西体育中心主体育场</t>
+          <t>广西体育中心体育场</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>青岛国信体育场</t>
+          <t>青岛国信体育中心体育场</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>福州海峡奥体中心体育场</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -18271,12 +18271,12 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>圣荷西</t>
+          <t>圣何塞</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>SAP Center</t>
+          <t>圣何塞SAP中心</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Smart Financial Center</t>
+          <t>Smart Financial Centre</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Barclays Center</t>
+          <t>纽约巴克莱中心</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Auditorium Theatre</t>
+          <t>芝加哥礼堂剧院</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Air Canada Centre</t>
+          <t>多伦多加拿大航空中心</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>虹口足球场</t>
+          <t>上海虹口足球场</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>桃园国际棒球场</t>
+          <t>乐天桃园棒球场</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>金光综艺馆（CotaiArena）</t>
+          <t>澳门威尼斯人金光综艺馆</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>AccorHotels Arena</t>
+          <t>巴黎雅高体育馆</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>The O2 Arena</t>
+          <t>伦敦O2体育馆</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>苏州体育中心体育场</t>
+          <t>苏州市体育中心体育场</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>贺龙体育中心体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>金华体育中心体育场</t>
+          <t>金华市体育中心体育场</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>河北奥体中心体育场</t>
+          <t>河北奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>佛山世纪莲体育中心</t>
+          <t>佛山世纪莲体育中心体育场</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Hisense Arena</t>
+          <t>John Cain Arena</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Qudos Bank Arena</t>
+          <t>库多斯银行体育馆</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>The Trusts Arena</t>
+          <t>奥克兰Trusts体育馆</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>桃园国际棒球场</t>
+          <t>乐天桃园棒球场</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>布鲁克林巴克莱中心</t>
+          <t>纽约巴克莱中心</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>杭州黄龙体育中心</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>武汉五环体育中心</t>
+          <t>武汉五环体育中心体育场</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心体育场</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>泉州海峡体育中心</t>
+          <t>泉州海峡体育中心体育场</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>西安奥体中心</t>
+          <t>西安奥体中心体育场</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>南京奥体中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>巴黎雅高竞技场</t>
+          <t>巴黎雅高体育馆</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>东安湖体育公园主体育场</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>启德主场馆</t>
+          <t>香港启德主场馆</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>贵阳市奥林匹克体育中心</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -20900,7 +20900,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>贺龙体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>郑州奥林匹克体育中心</t>
+          <t>郑州奥体中心体育场</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -20964,7 +20964,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>白鹭体育场</t>
+          <t>厦门奥林匹克体育中心-白鹭体育场</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>启德主场馆</t>
+          <t>香港启德主场馆</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>虹口足球场</t>
+          <t>上海虹口足球场</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场（大莲花）</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>呼和浩特市体育场</t>
+          <t>呼和浩特体育场</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>山西省体育中心体育场</t>
+          <t>山西体育中心体育场</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>兰州奥体中心玫瑰体育场</t>
+          <t>兰州奥体中心体育场</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -21508,7 +21508,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>苏州体育中心体育场</t>
+          <t>苏州市体育中心体育场</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>东安湖体育公园主体育场</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>亚洲国际博览馆Arena</t>
+          <t>亚洲国际博览馆</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>银河综艺馆</t>
+          <t>澳门银河综艺馆</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>常州奥体中心体育场</t>
+          <t>常州奥体中心新城体育场</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>厦门奥体中心白鹭体育场</t>
+          <t>厦门奥林匹克体育中心-白鹭体育场</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>金华体育中心体育场</t>
+          <t>金华市体育中心体育场</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场（大莲花）</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>佛山世纪莲体育中心</t>
+          <t>佛山世纪莲体育中心体育场</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>广州奥体中心体育场</t>
+          <t>广东奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>哈尔滨国际会展中心体育场</t>
+          <t>哈尔滨国际会展体育中心体育场</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心体育场</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>广州大学城体育中心</t>
+          <t>广州大学城体育中心体育场</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -22948,7 +22948,7 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>衢州体育中心体育场</t>
+          <t>衢州市体育中心体育场</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -22980,7 +22980,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>南京奥体中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>虹口足球场</t>
+          <t>上海虹口足球场</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>西安奥体中心</t>
+          <t>西安奥体中心体育场</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>鸟巢</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>沈阳奥体中心</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
@@ -23172,7 +23172,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>东安湖体育公园</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -23180,6 +23180,7 @@
           <t>2023-09-09</t>
         </is>
       </c>
+      <c r="F710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -23199,7 +23200,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>天河体育中心</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -23327,7 +23328,7 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>深圳大运中心</t>
+          <t>深圳大运中心体育场</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -23455,7 +23456,7 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>山西省体育中心体育场</t>
+          <t>山西体育中心体育场</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
@@ -23615,7 +23616,7 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -23711,7 +23712,7 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>兰州奥体中心玫瑰体育场</t>
+          <t>兰州奥体中心体育场</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -23807,7 +23808,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>深圳大运体育中心体育场</t>
+          <t>深圳大运中心体育场</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -23871,7 +23872,7 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>佛山世纪莲体育中心</t>
+          <t>佛山世纪莲体育中心体育场</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -23903,7 +23904,7 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>长沙贺龙体育中心体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -23999,7 +24000,7 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>青岛国信体育馆</t>
+          <t>青岛体育中心国信体育馆</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
@@ -24095,7 +24096,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>北京乐视体育生态中心</t>
+          <t>北京凯迪拉克中心</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -24159,7 +24160,7 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>武汉沌口体育馆</t>
+          <t>武汉体育中心体育馆</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -24255,7 +24256,7 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>鸟巢</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
@@ -24287,7 +24288,7 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>合肥体育中心主体育场</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -24319,7 +24320,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>南昌国际体育中心</t>
+          <t>南昌国际体育中心体育场</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -24351,7 +24352,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>沈阳奥体中心</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -24383,7 +24384,7 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>山西体育中心</t>
+          <t>山西体育中心体育场</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
@@ -24447,7 +24448,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>深圳大运中心</t>
+          <t>深圳大运中心体育场</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
@@ -24479,7 +24480,7 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>西安奥体中心</t>
+          <t>西安奥体中心体育场</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -24543,7 +24544,7 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>南京奥体中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
@@ -24575,7 +24576,7 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>海峡奥体中心</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
@@ -24607,7 +24608,7 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>重庆奥体中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -24639,7 +24640,7 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>台州体育中心体育场</t>
+          <t>台州市体育中心体育场</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -24703,7 +24704,7 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>广州奥体中心</t>
+          <t>广州大学城体育中心体育场</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -24713,7 +24714,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>3场·跨年</t>
+          <t>3场·跨年·收官</t>
         </is>
       </c>
     </row>
@@ -24735,7 +24736,7 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>郑州奥林匹克体育中心</t>
+          <t>郑州奥体中心体育场</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
@@ -24927,7 +24928,7 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>南京奥体中心主体育场</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -24959,7 +24960,7 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -25055,7 +25056,7 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>郑州奥林匹克体育中心体育馆</t>
+          <t>郑州奥体中心体育馆</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
@@ -25242,7 +25243,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>中国澳门</t>
+          <t>澳门</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -25311,7 +25312,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>墨尔本Rod Laver Arena</t>
+          <t>罗德·拉沃竞技场</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -25471,7 +25472,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>上海东方体育中心</t>
+          <t>浦发银行东方体育中心</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
@@ -25599,7 +25600,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>梅赛德斯-奔驰文化中心</t>
+          <t>上海梅赛德斯-奔驰文化中心</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -25631,7 +25632,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>深圳大运中心</t>
+          <t>深圳大运中心体育场</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -25639,6 +25640,7 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="F787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -25658,7 +25660,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>东安湖体育公园</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -25666,6 +25668,7 @@
           <t>2024-06-15</t>
         </is>
       </c>
+      <c r="F788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -25685,7 +25688,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>贵阳奥体中心</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -25693,6 +25696,7 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="F789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -25712,7 +25716,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -25720,6 +25724,7 @@
           <t>2024-07-27</t>
         </is>
       </c>
+      <c r="F790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -25739,7 +25744,7 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>南京奥体中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -25803,7 +25808,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>沈阳奥体中心</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -25811,6 +25816,7 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="F793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -25830,7 +25836,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>鸟巢</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
@@ -25862,7 +25868,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>重庆奥体中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -25894,7 +25900,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>苏州奥体中心</t>
+          <t>苏州奥体中心体育场</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -25926,7 +25932,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>南昌国际体育中心</t>
+          <t>南昌国际体育中心体育场</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
@@ -25934,6 +25940,7 @@
           <t>2024-11-23</t>
         </is>
       </c>
+      <c r="F797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -25953,7 +25960,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>广西体育中心</t>
+          <t>广西体育中心体育场</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -26145,7 +26152,7 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>哈尔滨国际会展中心体育场</t>
+          <t>哈尔滨国际会展体育中心体育场</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -26177,7 +26184,7 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>贵阳奥林匹克体育中心体育场</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -26337,7 +26344,7 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>合肥体育中心主体育场</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
@@ -26433,7 +26440,7 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>广东省奥林匹克中心体育场</t>
+          <t>广东奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -26465,7 +26472,7 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -26561,7 +26568,7 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>郑州奥林匹克体育中心体育场</t>
+          <t>郑州奥体中心体育场</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -26625,7 +26632,7 @@
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心体育场</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
@@ -26657,7 +26664,7 @@
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>贵阳奥林匹克体育中心体育场</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
@@ -26689,7 +26696,7 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>济南奥林匹克体育中心体育场</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
@@ -26817,7 +26824,7 @@
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>常州奥体中心体育场</t>
+          <t>常州奥体中心新城体育场</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
@@ -26849,7 +26856,7 @@
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>厦门奥林匹克体育中心白鹭体育场</t>
+          <t>厦门奥林匹克体育中心-白鹭体育场</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
@@ -26977,7 +26984,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>凯迪拉克中心</t>
+          <t>北京凯迪拉克中心</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
@@ -27073,7 +27080,7 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>深圳湾体育中心春蚕体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -27137,7 +27144,7 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>合肥奥林匹克体育中心</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
@@ -27169,7 +27176,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>贺龙体育中心体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
@@ -27361,7 +27368,7 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>东安湖体育公园主体育场</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
@@ -27457,7 +27464,7 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>奥林匹克体育中心郑地体育场</t>
+          <t>郑州奥体中心体育场</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
@@ -27489,7 +27496,7 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>福州海峡奥林匹克体育中心</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
@@ -27521,7 +27528,7 @@
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>哈尔滨国际会展中心体育场</t>
+          <t>哈尔滨国际会展体育中心体育场</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -27617,7 +27624,7 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>银河综艺馆</t>
+          <t>澳门银河综艺馆</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
@@ -27649,7 +27656,7 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
@@ -27777,7 +27784,7 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>武汉体育中心体育场</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
@@ -27873,7 +27880,7 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>苏州奥林匹克体育中心体育场</t>
+          <t>苏州奥体中心体育场</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -28129,7 +28136,7 @@
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>温布利体育馆</t>
+          <t>伦敦温布利体育馆</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -28289,7 +28296,7 @@
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>巴克莱中心</t>
+          <t>纽约巴克莱中心</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
@@ -28353,7 +28360,7 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>温州奥林匹克体育中心</t>
+          <t>温州奥体中心体育场</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -28609,7 +28616,7 @@
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>赣州市全民健身中心</t>
+          <t>赣州市全民健身中心体育场</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -28641,7 +28648,7 @@
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>启德主场馆</t>
+          <t>香港启德主场馆</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -28705,7 +28712,7 @@
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>东安湖体育公园主体育场</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -28737,7 +28744,7 @@
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>徐州市奥体中心主体育场</t>
+          <t>徐州奥体中心主体育场</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -28801,7 +28808,7 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>福州海峡奥体中心体育场</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -28865,7 +28872,7 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>三亚体育中心白鹭体育场</t>
+          <t>三亚市体育中心白鹭体育场</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
@@ -29025,7 +29032,7 @@
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>武吉加里尔国家体育场（马电讯国家体育场）</t>
+          <t>武吉加里尔国家体育场</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -29313,7 +29320,7 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>首都体育馆</t>
+          <t>北京首都体育馆</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -29377,7 +29384,7 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>南昌国际体育中心</t>
+          <t>南昌国际体育中心体育馆</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -29473,7 +29480,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>苏州市体育中心</t>
+          <t>苏州市体育中心体育馆</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -29633,7 +29640,7 @@
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>墨尔本海信体育馆（Hisense Arena）</t>
+          <t>John Cain Arena</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -29665,7 +29672,7 @@
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>悉尼国际会议中心剧场（ICC Theatre）</t>
+          <t>悉尼国际会议中心剧场</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -29697,7 +29704,7 @@
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>皇冠剧院（Crown Theatre）</t>
+          <t>珀斯皇冠剧院</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
@@ -29729,7 +29736,7 @@
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>布特拉室内体育馆</t>
+          <t>吉隆坡亚通体育馆</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -29793,7 +29800,7 @@
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>深圳湾体育中心</t>
+          <t>深圳湾体育中心“春茧”体育馆</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -29921,7 +29928,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>金光综艺馆</t>
+          <t>澳门威尼斯人金光综艺馆</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -30049,7 +30056,7 @@
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>成都演艺中心</t>
+          <t>成都五粮液演艺中心</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -30177,7 +30184,7 @@
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>梅赛德斯-奔驰文化中心</t>
+          <t>上海梅赛德斯-奔驰文化中心</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -30273,7 +30280,7 @@
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>金光综艺馆</t>
+          <t>澳门威尼斯人金光综艺馆</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -30305,7 +30312,7 @@
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>伊丽莎白女王剧院（Queen Elizabeth Theatre）</t>
+          <t>伊丽莎白女王剧院</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -30337,7 +30344,7 @@
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>可口可乐体育馆（Coca-Cola Coliseum）</t>
+          <t>可口可乐体育馆</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -30401,7 +30408,7 @@
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>云顶云星剧场（Arena of Stars）</t>
+          <t>云顶云星剧场</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -30561,7 +30568,7 @@
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>澳门金光综艺馆</t>
+          <t>澳门威尼斯人金光综艺馆</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -30625,7 +30632,7 @@
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>北京万事达中心</t>
+          <t>北京凯迪拉克中心</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -30657,7 +30664,7 @@
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>武汉沌口体育中心体育馆</t>
+          <t>武汉体育中心体育馆</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -30721,7 +30728,7 @@
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -30785,7 +30792,7 @@
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>杭州黄龙体育馆</t>
+          <t>杭州黄龙体育中心体育馆</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -30881,7 +30888,7 @@
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>大连市体育中心体育馆</t>
+          <t>大连体育中心体育馆</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
@@ -31137,7 +31144,7 @@
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心体育场</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
@@ -31201,7 +31208,7 @@
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>成都市体育中心体育场</t>
+          <t>成都体育中心体育场</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
@@ -31265,7 +31272,7 @@
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>南京奥林匹克体育中心体育场</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
@@ -31361,7 +31368,7 @@
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>济南奥林匹克体育中心体育馆</t>
+          <t>济南奥体中心东荷体育馆</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
@@ -31425,7 +31432,7 @@
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>吉隆坡布特拉室内体育馆</t>
+          <t>吉隆坡亚通体育馆</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
@@ -31937,7 +31944,7 @@
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>圣何塞思爱普中心</t>
+          <t>圣何塞SAP中心</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
@@ -31969,7 +31976,7 @@
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>洛杉矶论坛体育馆</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
@@ -32193,7 +32200,7 @@
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>Singapore Expo Hall1</t>
+          <t>新加坡博览中心</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
@@ -32289,7 +32296,7 @@
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>首都体育馆</t>
+          <t>北京首都体育馆</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
@@ -32353,7 +32360,7 @@
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>凯撒宫</t>
+          <t>凯撒宫大剧场</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -32449,7 +32456,7 @@
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>大阪 厚生年金会馆</t>
+          <t>大阪厚生年金会馆</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -32481,7 +32488,7 @@
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>东京 NHK大厅</t>
+          <t>东京NHK大厅</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -32673,7 +32680,7 @@
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>五台山体育场</t>
+          <t>南京五台山体育场</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
@@ -32897,7 +32904,7 @@
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>澳门威尼斯人 金光综艺馆</t>
+          <t>澳门威尼斯人金光综艺馆</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
@@ -33089,7 +33096,7 @@
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>新华路体育场</t>
+          <t>武汉新华路体育场</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
@@ -33121,7 +33128,7 @@
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>海峡体育场</t>
+          <t>泉州海峡体育中心体育场</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
@@ -33153,7 +33160,7 @@
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>重庆市奥林匹克体育中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
@@ -33185,7 +33192,7 @@
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
@@ -33249,7 +33256,7 @@
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>南京奥林匹克体育中心</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
@@ -33313,7 +33320,7 @@
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>成都市体育中心</t>
+          <t>成都体育中心体育场</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
@@ -33345,7 +33352,7 @@
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>常州奥林匹克体育中心</t>
+          <t>常州奥体中心新城体育场</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
@@ -33377,7 +33384,7 @@
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>合肥奥林匹克体育中心</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
@@ -33409,7 +33416,7 @@
       </c>
       <c r="D1031" t="inlineStr">
         <is>
-          <t>黄龙体育中心体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E1031" t="inlineStr">
@@ -33441,7 +33448,7 @@
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>天河体育中心体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
@@ -33473,7 +33480,7 @@
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>济南奥林匹克体育中心体育场</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
@@ -33633,7 +33640,7 @@
       </c>
       <c r="D1038" t="inlineStr">
         <is>
-          <t>国家体育场</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E1038" t="inlineStr">
@@ -33665,7 +33672,7 @@
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>武汉体育中心体育场</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E1039" t="inlineStr">
@@ -33697,7 +33704,7 @@
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>南通体育会展中心梦之蓝体育场</t>
+          <t>南通体育会展中心体育场</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
@@ -33729,7 +33736,7 @@
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
@@ -33857,7 +33864,7 @@
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>五象新区广西区体育中心</t>
+          <t>广西体育中心体育场</t>
         </is>
       </c>
       <c r="E1045" t="inlineStr">
@@ -33921,7 +33928,7 @@
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>哈尔滨国际会展中心体育场</t>
+          <t>哈尔滨国际会展体育中心体育场</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
@@ -33985,7 +33992,7 @@
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>贺龙体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
@@ -34049,7 +34056,7 @@
       </c>
       <c r="D1051" t="inlineStr">
         <is>
-          <t>合肥奥林匹克体育中心</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E1051" t="inlineStr">
@@ -34081,7 +34088,7 @@
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>福州省体育中心</t>
+          <t>福建省体育中心体育场</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
@@ -34113,7 +34120,7 @@
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>贵阳市奥林匹克体育中心</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
@@ -34177,7 +34184,7 @@
       </c>
       <c r="D1055" t="inlineStr">
         <is>
-          <t>重庆市奥林匹克体育中心</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E1055" t="inlineStr">
@@ -34209,7 +34216,7 @@
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>泉州市海峡体育中心体育场</t>
+          <t>泉州海峡体育中心体育场</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
@@ -34241,7 +34248,7 @@
       </c>
       <c r="D1057" t="inlineStr">
         <is>
-          <t>佛山世纪莲体育中心</t>
+          <t>佛山世纪莲体育中心体育场</t>
         </is>
       </c>
       <c r="E1057" t="inlineStr">
@@ -34369,7 +34376,7 @@
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>Sydney Entertainment Centre</t>
+          <t>悉尼娱乐中心</t>
         </is>
       </c>
       <c r="E1061" t="inlineStr">
@@ -34401,7 +34408,7 @@
       </c>
       <c r="D1062" t="inlineStr">
         <is>
-          <t>Melbourne Exhibition Centre</t>
+          <t>墨尔本会展中心</t>
         </is>
       </c>
       <c r="E1062" t="inlineStr">
@@ -34497,7 +34504,7 @@
       </c>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>杭州黄龙体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
@@ -34593,7 +34600,7 @@
       </c>
       <c r="D1068" t="inlineStr">
         <is>
-          <t>河南省体育中心</t>
+          <t>河南省体育中心体育场</t>
         </is>
       </c>
       <c r="E1068" t="inlineStr">
@@ -34657,7 +34664,7 @@
       </c>
       <c r="D1070" t="inlineStr">
         <is>
-          <t>天河体育中心体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E1070" t="inlineStr">
@@ -34721,7 +34728,7 @@
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>五象新区广西区体育场</t>
+          <t>广西体育场</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
@@ -34817,7 +34824,7 @@
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
@@ -34881,7 +34888,7 @@
       </c>
       <c r="D1077" t="inlineStr">
         <is>
-          <t>江西省奥林匹克体育中心体育场</t>
+          <t>江西省奥体中心体育场</t>
         </is>
       </c>
       <c r="E1077" t="inlineStr">
@@ -34913,7 +34920,7 @@
       </c>
       <c r="D1078" t="inlineStr">
         <is>
-          <t>裕彤国际体育中心</t>
+          <t>石家庄裕彤国际体育中心</t>
         </is>
       </c>
       <c r="E1078" t="inlineStr">
@@ -34945,7 +34952,7 @@
       </c>
       <c r="D1079" t="inlineStr">
         <is>
-          <t>成都体育中心</t>
+          <t>成都体育中心体育场</t>
         </is>
       </c>
       <c r="E1079" t="inlineStr">
@@ -35009,7 +35016,7 @@
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>黄龙体育中心体育场</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E1081" t="inlineStr">
@@ -35073,7 +35080,7 @@
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>国家体育场</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
@@ -35233,7 +35240,7 @@
       </c>
       <c r="D1088" t="inlineStr">
         <is>
-          <t>成都双流体育中心</t>
+          <t>成都双流体育中心体育场</t>
         </is>
       </c>
       <c r="E1088" t="inlineStr">
@@ -35265,7 +35272,7 @@
       </c>
       <c r="D1089" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E1089" t="inlineStr">
@@ -35329,7 +35336,7 @@
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>杭州黄龙体育中心</t>
+          <t>杭州黄龙体育中心体育场</t>
         </is>
       </c>
       <c r="E1091" t="inlineStr">
@@ -35489,7 +35496,7 @@
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>金华体育中心体育场</t>
+          <t>金华市体育中心体育场</t>
         </is>
       </c>
       <c r="E1096" t="inlineStr">
@@ -35521,7 +35528,7 @@
       </c>
       <c r="D1097" t="inlineStr">
         <is>
-          <t>珠海体育中心体育场</t>
+          <t>珠海市体育中心体育场</t>
         </is>
       </c>
       <c r="E1097" t="inlineStr">
@@ -35649,7 +35656,7 @@
       </c>
       <c r="D1101" t="inlineStr">
         <is>
-          <t>吉隆坡默迪卡体育场</t>
+          <t>默迪卡体育场</t>
         </is>
       </c>
       <c r="E1101" t="inlineStr">
@@ -35681,7 +35688,7 @@
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>惠州奥林匹克体育中心体育场</t>
+          <t>惠州奥林匹克体育场</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
@@ -35809,7 +35816,7 @@
       </c>
       <c r="D1106" t="inlineStr">
         <is>
-          <t>徐州奥林匹克体育中心体育场</t>
+          <t>徐州奥体中心主体育场</t>
         </is>
       </c>
       <c r="E1106" t="inlineStr">
@@ -36001,7 +36008,7 @@
       </c>
       <c r="D1112" t="inlineStr">
         <is>
-          <t>杭州奥体博览中心主体育场</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1112" t="inlineStr">
@@ -36097,7 +36104,7 @@
       </c>
       <c r="D1115" t="inlineStr">
         <is>
-          <t>青岛国信体育场</t>
+          <t>青岛国信体育中心体育场</t>
         </is>
       </c>
       <c r="E1115" t="inlineStr">
@@ -36193,7 +36200,7 @@
       </c>
       <c r="D1118" t="inlineStr">
         <is>
-          <t>贵阳奥林匹克体育中心体育场</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E1118" t="inlineStr">
@@ -36417,7 +36424,7 @@
       </c>
       <c r="D1125" t="inlineStr">
         <is>
-          <t>南昌国际体育中心综合体育馆</t>
+          <t>南昌国际体育中心体育馆</t>
         </is>
       </c>
       <c r="E1125" t="inlineStr">
@@ -36449,7 +36456,7 @@
       </c>
       <c r="D1126" t="inlineStr">
         <is>
-          <t>宝能广州国际体育演艺中心</t>
+          <t>广州国际体育演艺中心</t>
         </is>
       </c>
       <c r="E1126" t="inlineStr">
@@ -36513,7 +36520,7 @@
       </c>
       <c r="D1128" t="inlineStr">
         <is>
-          <t>华熙LIVE·五棵松</t>
+          <t>北京凯迪拉克中心</t>
         </is>
       </c>
       <c r="E1128" t="inlineStr">
@@ -36641,7 +36648,7 @@
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>梅赛德斯-奔驰文化中心</t>
+          <t>上海梅赛德斯-奔驰文化中心</t>
         </is>
       </c>
       <c r="E1132" t="inlineStr">
@@ -36673,7 +36680,7 @@
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>华熙LIVE·鱼洞</t>
+          <t>重庆华熙LIVE·鱼洞文体中心</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
@@ -36833,7 +36840,7 @@
       </c>
       <c r="D1138" t="inlineStr">
         <is>
-          <t>少荃体育中心体育馆</t>
+          <t>合肥少荃体育中心体育馆</t>
         </is>
       </c>
       <c r="E1138" t="inlineStr">
@@ -37057,7 +37064,7 @@
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>Qudos Bank Arena</t>
+          <t>库多斯银行体育馆</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
@@ -37089,7 +37096,7 @@
       </c>
       <c r="D1146" t="inlineStr">
         <is>
-          <t>Rod Laver Arena</t>
+          <t>罗德·拉沃竞技场</t>
         </is>
       </c>
       <c r="E1146" t="inlineStr">
@@ -37217,7 +37224,7 @@
       </c>
       <c r="D1150" t="inlineStr">
         <is>
-          <t>苏州奥林匹克体育中心体育场</t>
+          <t>苏州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
@@ -37345,7 +37352,7 @@
       </c>
       <c r="D1154" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>武汉五环体育中心体育馆</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
@@ -37377,7 +37384,7 @@
       </c>
       <c r="D1155" t="inlineStr">
         <is>
-          <t>白鹭体育场</t>
+          <t>厦门嘉庚体育馆</t>
         </is>
       </c>
       <c r="E1155" t="inlineStr">
@@ -37404,22 +37411,22 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>佛山</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
-          <t>华熙LIVE·五棵松</t>
+          <t>佛山岭南明珠体育馆</t>
         </is>
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37436,22 +37443,22 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>无锡</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
         <is>
-          <t>南京奥体中心</t>
+          <t>无锡体育中心体育馆</t>
         </is>
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="F1157" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37468,17 +37475,17 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="D1158" t="inlineStr">
         <is>
-          <t>天津奥体中心体育场</t>
+          <t>青岛体育中心国信体育馆</t>
         </is>
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="F1158" t="inlineStr">
@@ -37500,22 +37507,22 @@
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D1159" t="inlineStr">
         <is>
-          <t>梅赛德斯-奔驰文化中心</t>
+          <t>北京凯迪拉克中心</t>
         </is>
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="F1159" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>3场</t>
         </is>
       </c>
     </row>
@@ -37532,22 +37539,22 @@
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
-          <t>重庆奥体中心</t>
+          <t>南京青奥体育公园体育馆</t>
         </is>
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="F1160" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>3场</t>
         </is>
       </c>
     </row>
@@ -37564,17 +37571,17 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南宁</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
         <is>
-          <t>广州奥体中心</t>
+          <t>广西体育中心体育馆</t>
         </is>
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="F1161" t="inlineStr">
@@ -37596,22 +37603,22 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>东安湖体育公园</t>
+          <t>天津奥体中心体育馆</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="F1162" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37628,22 +37635,22 @@
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南昌</t>
         </is>
       </c>
       <c r="D1163" t="inlineStr">
         <is>
-          <t>深圳大运中心</t>
+          <t>南昌国际体育中心体育馆</t>
         </is>
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="F1163" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37660,17 +37667,17 @@
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D1164" t="inlineStr">
         <is>
-          <t>西安奥体中心</t>
+          <t>上海梅赛德斯-奔驰文化中心</t>
         </is>
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="F1164" t="inlineStr">
@@ -37692,22 +37699,22 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场</t>
+          <t>重庆华熙LIVE·鱼洞文体中心</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="F1165" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37724,22 +37731,22 @@
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>泉州</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
-          <t>国家体育场鸟巢</t>
+          <t>晋江市第二体育中心体育馆</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="F1166" t="inlineStr">
         <is>
-          <t>3场·内地收官</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37751,27 +37758,27 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Soul Power II PLUS世界巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>郑州奥体中心体育馆</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="F1167" t="inlineStr">
         <is>
-          <t>3场·Plus首站</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37783,27 +37790,27 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Soul Power II PLUS世界巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁波</t>
         </is>
       </c>
       <c r="D1168" t="inlineStr">
         <is>
-          <t>天津奥体中心体育场</t>
+          <t>宁波奥体中心体育馆</t>
         </is>
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="F1168" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37815,27 +37822,27 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Soul Power II PLUS世界巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>广州天河体育中心体育场</t>
+          <t>台北小巨蛋</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="F1169" t="inlineStr">
         <is>
-          <t>3场·Plus</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37847,27 +37854,27 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Soul Power II PLUS世界巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>合肥</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>重庆奥体中心体育场</t>
+          <t>合肥少荃体育中心体育馆</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="F1170" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37879,27 +37886,27 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Soul Power II PLUS世界巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
-          <t>上海虹口足球场</t>
+          <t>广州海心沙亚运公园</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t>6场·Plus·收官·第100场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37911,7 +37918,7 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Soul Power巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
@@ -37926,12 +37933,12 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>2003-08-14</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="F1172" t="inlineStr">
         <is>
-          <t>3场·首站</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37943,27 +37950,27 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Soul Power巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
         <is>
-          <t>台北市立体育场</t>
+          <t>苏州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>2003-11-22</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="F1173" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -37975,27 +37982,27 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Soul Power巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>新加坡</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D1174" t="inlineStr">
         <is>
-          <t>新加坡室内体育馆</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>2003-12-10</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t>1场·收官</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -38007,22 +38014,22 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>就是爱你音乐惊奇之旅巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵阳</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
         <is>
-          <t>上海虹口足球场</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>2005-08-13</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="F1175" t="inlineStr">
@@ -38039,22 +38046,22 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>就是爱你音乐惊奇之旅巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
-          <t>台北小巨蛋</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>2006-01-21</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="F1176" t="inlineStr">
@@ -38071,22 +38078,22 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>123我们都是木头人巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>长沙</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
-          <t>台北小巨蛋</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>2007-10-26</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="F1177" t="inlineStr">
@@ -38103,22 +38110,22 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>小人物狂想曲巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>济南</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
-          <t>上海虹口足球场</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>2013-05-25</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="F1178" t="inlineStr">
@@ -38135,118 +38142,118 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>小人物狂想曲巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>沈阳</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
         <is>
-          <t>南京奥体中心体育场</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="F1179" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
-          <t>武汉体育中心体育场</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="F1180" t="inlineStr">
         <is>
-          <t>1场·首站</t>
+          <t>3场</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
-          <t>深圳湾体育中心体育场</t>
+          <t>西安奥体中心体育场</t>
         </is>
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="F1181" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>合肥</t>
+          <t>哈尔滨</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>合肥奥体中心体育场</t>
+          <t>哈尔滨国际会展体育中心体育场</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="F1182" t="inlineStr">
@@ -38258,155 +38265,155 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
-          <t>南京奥体中心体育场</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="F1183" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>3场</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>常州</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
         <is>
-          <t>成都凤凰山体育公园专业足球场</t>
+          <t>常州奥体中心新城体育场</t>
         </is>
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F1184" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>3场</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>大连</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
         <is>
-          <t>大连体育中心体育场</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="F1185" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>3场·内地收官</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>吉隆坡</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场</t>
+          <t>吉隆坡亚通体育馆</t>
         </is>
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>太原</t>
+          <t>悉尼</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
-          <t>山西体育中心体育场</t>
+          <t>库多斯银行体育馆</t>
         </is>
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="F1187" t="inlineStr">
@@ -38418,27 +38425,27 @@
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>郑州</t>
+          <t>墨尔本</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
-          <t>郑州奥林匹克体育中心体育场</t>
+          <t>罗德·拉沃竞技场</t>
         </is>
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="F1188" t="inlineStr">
@@ -38450,27 +38457,27 @@
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>温哥华</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
-          <t>重庆市奥林匹克体育中心体育场</t>
+          <t>Doug Mitchell Thunderbird Sports Centre</t>
         </is>
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="F1189" t="inlineStr">
@@ -38482,27 +38489,27 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>康涅狄格州</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
-          <t>苏州奥体中心体育场</t>
+          <t>康涅狄格金神体育馆</t>
         </is>
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F1190" t="inlineStr">
@@ -38514,27 +38521,27 @@
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>长沙</t>
+          <t>纽约</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
-          <t>长沙贺龙体育场</t>
+          <t>纽约巴克莱中心</t>
         </is>
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="F1191" t="inlineStr">
@@ -38546,27 +38553,27 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>休斯顿</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
-          <t>南京奥体中心体育场</t>
+          <t>Smart Financial Centre</t>
         </is>
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F1192" t="inlineStr">
@@ -38578,27 +38585,27 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>多伦多</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
-          <t>深圳大运中心体育场</t>
+          <t>可口可乐体育馆</t>
         </is>
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F1193" t="inlineStr">
@@ -38610,59 +38617,59 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>湖州</t>
+          <t>洛杉矶</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
         <is>
-          <t>湖州奥体中心体育场</t>
+          <t>Kia Forum</t>
         </is>
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F1194" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>厦门</t>
+          <t>伦敦</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
         <is>
-          <t>厦门奥林匹克体育中心白鹭体育场</t>
+          <t>伦敦温布利体育馆</t>
         </is>
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="F1195" t="inlineStr">
@@ -38674,76 +38681,76 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>巴黎</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
         <is>
-          <t>天津奥体中心体育场</t>
+          <t>巴黎天顶体育馆</t>
         </is>
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="F1196" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II 世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>镇江</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
         <is>
-          <t>镇江市体育会展中心</t>
+          <t>新加坡室内体育馆</t>
         </is>
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="F1197" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>1场·海外最终站</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II PLUS世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
@@ -38753,300 +38760,300 @@
       </c>
       <c r="D1198" t="inlineStr">
         <is>
-          <t>武汉体育中心</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="F1198" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>3场·Plus首站</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II PLUS世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>徐州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
         <is>
-          <t>徐州奥体中心主体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="F1199" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>3场</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II PLUS世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
         <is>
-          <t>成都东安湖体育公园主体育场</t>
+          <t>广州天河体育中心体育场</t>
         </is>
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F1200" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>3场·Plus</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II PLUS世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D1201" t="inlineStr">
         <is>
-          <t>济南奥体中心体育场</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F1201" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>3场</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power II PLUS世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场（大莲花）</t>
+          <t>上海虹口足球场</t>
         </is>
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F1202" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>6场·Plus·收官·第100场</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>呼吸之野巡回演唱会</t>
+          <t>Soul Power巡回演唱会</t>
         </is>
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>合肥</t>
+          <t>香港</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
         <is>
-          <t>合肥体育中心</t>
+          <t>红磡体育馆</t>
         </is>
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2003-08-14</t>
         </is>
       </c>
       <c r="F1203" t="inlineStr">
         <is>
-          <t>1场·收官·第40场</t>
+          <t>3场·首站</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>安泊猜想巡回演唱会</t>
+          <t>Soul Power巡回演唱会</t>
         </is>
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场（大莲花）</t>
+          <t>台北市立体育场</t>
         </is>
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2003-11-22</t>
         </is>
       </c>
       <c r="F1204" t="inlineStr">
         <is>
-          <t>2场·首站</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>安泊猜想巡回演唱会</t>
+          <t>Soul Power巡回演唱会</t>
         </is>
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>新加坡</t>
         </is>
       </c>
       <c r="D1205" t="inlineStr">
         <is>
-          <t>武汉体育中心主体育场</t>
+          <t>新加坡室内体育馆</t>
         </is>
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2003-12-10</t>
         </is>
       </c>
       <c r="F1205" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场·收官</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>安泊猜想巡回演唱会</t>
+          <t>就是爱你音乐惊奇之旅巡回演唱会</t>
         </is>
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D1206" t="inlineStr">
         <is>
-          <t>广东省奥林匹克中心体育场</t>
+          <t>上海虹口足球场</t>
         </is>
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2005-08-13</t>
         </is>
       </c>
       <c r="F1206" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>安泊猜想巡回演唱会</t>
+          <t>就是爱你音乐惊奇之旅巡回演唱会</t>
         </is>
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>洛阳</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
         <is>
-          <t>洛阳市奥林匹克中心体育场</t>
+          <t>台北小巨蛋</t>
         </is>
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2006-01-21</t>
         </is>
       </c>
       <c r="F1207" t="inlineStr">
@@ -39058,27 +39065,27 @@
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>安泊猜想巡回演唱会</t>
+          <t>123我们都是木头人巡回演唱会</t>
         </is>
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>青岛</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="D1208" t="inlineStr">
         <is>
-          <t>青岛市民健身中心体育场</t>
+          <t>台北小巨蛋</t>
         </is>
       </c>
       <c r="E1208" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2007-10-26</t>
         </is>
       </c>
       <c r="F1208" t="inlineStr">
@@ -39090,64 +39097,64 @@
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>安泊猜想巡回演唱会</t>
+          <t>小人物狂想曲巡回演唱会</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
         <is>
-          <t>天津奥体中心体育场</t>
+          <t>上海虹口足球场</t>
         </is>
       </c>
       <c r="E1209" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2013-05-25</t>
         </is>
       </c>
       <c r="F1209" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>许嵩</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>安泊猜想巡回演唱会</t>
+          <t>小人物狂想曲巡回演唱会</t>
         </is>
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D1210" t="inlineStr">
         <is>
-          <t>苏州奥林匹克体育中心体育场</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E1210" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="F1210" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
@@ -39159,27 +39166,27 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>青年晚报巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
         <is>
-          <t>上海体育馆</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>2017-03-18</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="F1211" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>1场·首站</t>
         </is>
       </c>
     </row>
@@ -39191,22 +39198,22 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>青年晚报巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D1212" t="inlineStr">
         <is>
-          <t>北京首都体育馆</t>
+          <t>深圳湾体育中心“春茧”体育场</t>
         </is>
       </c>
       <c r="E1212" t="inlineStr">
         <is>
-          <t>2017-07-15</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="F1212" t="inlineStr">
@@ -39223,22 +39230,22 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>青年晚报巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>合肥</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
         <is>
-          <t>南京五台山体育馆</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E1213" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="F1213" t="inlineStr">
@@ -39255,22 +39262,22 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>青年晚报巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
         <is>
-          <t>广州体育馆</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>2017-10-07</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="F1214" t="inlineStr">
@@ -39287,7 +39294,7 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>寻宝游戏巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
@@ -39297,17 +39304,17 @@
       </c>
       <c r="D1215" t="inlineStr">
         <is>
-          <t>五粮液成都金融城演艺中心</t>
+          <t>成都凤凰山体育公园专业足球场</t>
         </is>
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="F1215" t="inlineStr">
         <is>
-          <t>1场·首站</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
@@ -39319,22 +39326,22 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>寻宝游戏巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>大连</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
         <is>
-          <t>光谷国际网球中心</t>
+          <t>大连体育中心体育场</t>
         </is>
       </c>
       <c r="E1216" t="inlineStr">
         <is>
-          <t>2019-06-08</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="F1216" t="inlineStr">
@@ -39351,22 +39358,22 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>寻宝游戏巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
         <is>
-          <t>梅赛德斯奔驰文化中心</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>2019-06-22</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="F1217" t="inlineStr">
@@ -39383,22 +39390,22 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>寻宝游戏巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>太原</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
         <is>
-          <t>凯迪拉克中心</t>
+          <t>山西体育中心体育场</t>
         </is>
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="F1218" t="inlineStr">
@@ -39415,86 +39422,86 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>寻宝游戏巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>合肥</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="D1219" t="inlineStr">
         <is>
-          <t>合肥体育中心体育馆</t>
+          <t>郑州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>2019-07-20</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="F1219" t="inlineStr">
         <is>
-          <t>1场·收官</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
         <is>
-          <t>南京奥林匹克体育中心体育场</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="F1220" t="inlineStr">
         <is>
-          <t>1场·首站</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr">
         <is>
-          <t>西安奥林匹克体育中心体育场</t>
+          <t>苏州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="F1221" t="inlineStr">
@@ -39506,12 +39513,12 @@
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1222" t="inlineStr">
@@ -39521,12 +39528,12 @@
       </c>
       <c r="D1222" t="inlineStr">
         <is>
-          <t>长沙贺龙体育中心体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="F1222" t="inlineStr">
@@ -39538,27 +39545,27 @@
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>沈阳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心体育场</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="F1223" t="inlineStr">
@@ -39570,59 +39577,59 @@
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>石家庄</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D1224" t="inlineStr">
         <is>
-          <t>河北奥林匹克体育中心体育场</t>
+          <t>深圳大运中心体育场</t>
         </is>
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F1224" t="inlineStr">
         <is>
-          <t>1场·原4/12因天气延期</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>常州</t>
+          <t>湖州</t>
         </is>
       </c>
       <c r="D1225" t="inlineStr">
         <is>
-          <t>常州奥林匹克体育中心体育场</t>
+          <t>湖州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="F1225" t="inlineStr">
@@ -39634,27 +39641,27 @@
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="D1226" t="inlineStr">
         <is>
-          <t>武汉体育中心体育场</t>
+          <t>厦门奥林匹克体育中心-白鹭体育场</t>
         </is>
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="F1226" t="inlineStr">
@@ -39666,27 +39673,27 @@
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D1227" t="inlineStr">
         <is>
-          <t>上海虹口足球场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="F1227" t="inlineStr">
@@ -39698,27 +39705,27 @@
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>绍兴</t>
+          <t>镇江</t>
         </is>
       </c>
       <c r="D1228" t="inlineStr">
         <is>
-          <t>中国轻纺城体育中心体育场</t>
+          <t>镇江体育会展中心体育场</t>
         </is>
       </c>
       <c r="E1228" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="F1228" t="inlineStr">
@@ -39730,27 +39737,27 @@
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>厦门</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D1229" t="inlineStr">
         <is>
-          <t>厦门奥林匹克体育中心白鹭体育场</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="F1229" t="inlineStr">
@@ -39762,27 +39769,27 @@
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>合肥</t>
+          <t>徐州</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
         <is>
-          <t>合肥体育中心体育场</t>
+          <t>徐州奥体中心主体育场</t>
         </is>
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="F1230" t="inlineStr">
@@ -39794,27 +39801,27 @@
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
         <is>
-          <t>济南奥体中心体育场</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="F1231" t="inlineStr">
@@ -39826,27 +39833,27 @@
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>南昌</t>
+          <t>济南</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
         <is>
-          <t>南昌国际体育中心体育场</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="F1232" t="inlineStr">
@@ -39858,219 +39865,219 @@
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D1233" t="inlineStr">
         <is>
-          <t>重庆奥林匹克体育中心体育场</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="F1233" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>呼吸之野巡回演唱会</t>
         </is>
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>悉尼</t>
+          <t>合肥</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
         <is>
-          <t>ICC Sydney Theatre</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="F1234" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>1场·收官·第40场</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>安泊猜想巡回演唱会</t>
         </is>
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>墨尔本</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
         <is>
-          <t>John Cain Arena</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="F1235" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场·首站</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>安泊猜想巡回演唱会</t>
         </is>
       </c>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>奥克兰</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr">
         <is>
-          <t>The Trusts Arena</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F1236" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>安泊猜想巡回演唱会</t>
         </is>
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>清远</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
         <is>
-          <t>清远体育中心体育场</t>
+          <t>广东奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F1237" t="inlineStr">
         <is>
-          <t>3场·跨年</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>安泊猜想巡回演唱会</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>太原</t>
+          <t>洛阳</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
         <is>
-          <t>山西体育中心体育场</t>
+          <t>洛阳市奥林匹克中心体育场</t>
         </is>
       </c>
       <c r="E1238" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F1238" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>安泊猜想巡回演唱会</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场（大莲花）</t>
+          <t>青岛市民健身中心体育场</t>
         </is>
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F1239" t="inlineStr">
@@ -40082,59 +40089,59 @@
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>安泊猜想巡回演唱会</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>哈尔滨</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
         <is>
-          <t>哈尔滨国际会展体育中心体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F1240" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>安泊猜想巡回演唱会</t>
         </is>
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>南宁</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
         <is>
-          <t>广西体育中心体育场</t>
+          <t>苏州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1241" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F1241" t="inlineStr">
@@ -40146,59 +40153,59 @@
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>青年晚报巡回演唱会</t>
         </is>
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>贵阳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
         <is>
-          <t>贵阳奥林匹克体育中心体育场</t>
+          <t>上海体育馆</t>
         </is>
       </c>
       <c r="E1242" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2017-03-18</t>
         </is>
       </c>
       <c r="F1242" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>青年晚报巡回演唱会</t>
         </is>
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>呼和浩特</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
         <is>
-          <t>呼和浩特体育场</t>
+          <t>北京首都体育馆</t>
         </is>
       </c>
       <c r="E1243" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2017-07-15</t>
         </is>
       </c>
       <c r="F1243" t="inlineStr">
@@ -40210,59 +40217,59 @@
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>青年晚报巡回演唱会</t>
         </is>
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D1244" t="inlineStr">
         <is>
-          <t>苏州奥林匹克体育中心体育场</t>
+          <t>南京五台山体育馆</t>
         </is>
       </c>
       <c r="E1244" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="F1244" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>青年晚报巡回演唱会</t>
         </is>
       </c>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>赣州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
         <is>
-          <t>赣州市全民健身中心体育场</t>
+          <t>广州体育馆</t>
         </is>
       </c>
       <c r="E1245" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2017-10-07</t>
         </is>
       </c>
       <c r="F1245" t="inlineStr">
@@ -40274,59 +40281,59 @@
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>寻宝游戏巡回演唱会</t>
         </is>
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>襄阳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
         <is>
-          <t>襄阳奥林匹克体育中心</t>
+          <t>成都五粮液演艺中心</t>
         </is>
       </c>
       <c r="E1246" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="F1246" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>1场·首站</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>寻宝游戏巡回演唱会</t>
         </is>
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>大连</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
         <is>
-          <t>大连体育中心体育场</t>
+          <t>武汉光谷国际网球中心</t>
         </is>
       </c>
       <c r="E1247" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2019-06-08</t>
         </is>
       </c>
       <c r="F1247" t="inlineStr">
@@ -40338,27 +40345,27 @@
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>寻宝游戏巡回演唱会</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>乌鲁木齐</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
         <is>
-          <t>乌鲁木齐奥体中心体育场</t>
+          <t>上海梅赛德斯-奔驰文化中心</t>
         </is>
       </c>
       <c r="E1248" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="F1248" t="inlineStr">
@@ -40370,64 +40377,64 @@
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>寻宝游戏巡回演唱会</t>
         </is>
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
         <is>
-          <t>成都东安湖体育公园主体育场</t>
+          <t>北京凯迪拉克中心</t>
         </is>
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2019-07-06</t>
         </is>
       </c>
       <c r="F1249" t="inlineStr">
         <is>
-          <t>2场·含9/6加场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>李荣浩</t>
+          <t>许嵩</t>
         </is>
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>黑马巡回演唱会</t>
+          <t>寻宝游戏巡回演唱会</t>
         </is>
       </c>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>合肥</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
         <is>
-          <t>上海体育场</t>
+          <t>合肥体育中心体育馆</t>
         </is>
       </c>
       <c r="E1250" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2019-07-20</t>
         </is>
       </c>
       <c r="F1250" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场·收官</t>
         </is>
       </c>
     </row>
@@ -40444,22 +40451,22 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>临沂</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
         <is>
-          <t>临沂奥体公园体育场</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E1251" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="F1251" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>1场·首站</t>
         </is>
       </c>
     </row>
@@ -40476,22 +40483,22 @@
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
         <is>
-          <t>天津奥体中心体育场</t>
+          <t>西安奥体中心体育场</t>
         </is>
       </c>
       <c r="E1252" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="F1252" t="inlineStr">
         <is>
-          <t>3场·原7/10-12因台风延期</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
@@ -40508,17 +40515,17 @@
       </c>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>衡阳</t>
+          <t>长沙</t>
         </is>
       </c>
       <c r="D1253" t="inlineStr">
         <is>
-          <t>衡阳市体育中心体育场</t>
+          <t>长沙贺龙体育场</t>
         </is>
       </c>
       <c r="E1253" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="F1253" t="inlineStr">
@@ -40540,22 +40547,22 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>郑州</t>
+          <t>沈阳</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
         <is>
-          <t>郑州奥林匹克体育中心体育场</t>
+          <t>沈阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="F1254" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
@@ -40572,22 +40579,22 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>石家庄</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
         <is>
-          <t>福州海峡奥体中心体育场中心赛场</t>
+          <t>河北奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E1255" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="F1255" t="inlineStr">
         <is>
-          <t>1场·原10/17延期</t>
+          <t>1场·原4/12因天气延期</t>
         </is>
       </c>
     </row>
@@ -40599,22 +40606,22 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>年少有为世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>厦门</t>
+          <t>常州</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
         <is>
-          <t>厦门嘉庚体育馆</t>
+          <t>常州奥体中心新城体育场</t>
         </is>
       </c>
       <c r="E1256" t="inlineStr">
         <is>
-          <t>2019-03-30</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="F1256" t="inlineStr">
@@ -40631,22 +40638,22 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>年少有为世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>大连</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
         <is>
-          <t>大连体育中心体育馆</t>
+          <t>武汉体育中心主体育场</t>
         </is>
       </c>
       <c r="E1257" t="inlineStr">
         <is>
-          <t>2019-04-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="F1257" t="inlineStr">
@@ -40663,27 +40670,27 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>年少有为世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>青岛</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D1258" t="inlineStr">
         <is>
-          <t>青岛市体育中心国信体育馆</t>
+          <t>上海虹口足球场</t>
         </is>
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="F1258" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -40695,22 +40702,22 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>年少有为世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>合肥</t>
+          <t>绍兴</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
         <is>
-          <t>合肥滨湖国际会展中心主展馆</t>
+          <t>中国轻纺城体育中心体育场</t>
         </is>
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>2019-07-27</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="F1259" t="inlineStr">
@@ -40727,22 +40734,22 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>年少有为世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
         <is>
-          <t>武汉体育中心体育馆</t>
+          <t>厦门奥林匹克体育中心-白鹭体育场</t>
         </is>
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>2019-12-14</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="F1260" t="inlineStr">
@@ -40759,22 +40766,22 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>年少有为世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>合肥</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
         <is>
-          <t>重庆国际博览中心</t>
+          <t>合肥体育中心体育场</t>
         </is>
       </c>
       <c r="E1261" t="inlineStr">
         <is>
-          <t>2019-12-21</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="F1261" t="inlineStr">
@@ -40791,27 +40798,27 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>麻雀巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>济南</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
         <is>
-          <t>南京奥体中心体育场</t>
+          <t>济南奥体中心体育场</t>
         </is>
       </c>
       <c r="E1262" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="F1262" t="inlineStr">
         <is>
-          <t>首站</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
@@ -40823,22 +40830,22 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>纵横四海世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>南昌</t>
         </is>
       </c>
       <c r="D1263" t="inlineStr">
         <is>
-          <t>南京奥体中心体育场</t>
+          <t>南昌国际体育中心体育场</t>
         </is>
       </c>
       <c r="E1263" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="F1263" t="inlineStr">
@@ -40855,22 +40862,22 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>纵横四海世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场</t>
+          <t>重庆奥体中心体育场</t>
         </is>
       </c>
       <c r="E1264" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F1264" t="inlineStr">
@@ -40887,27 +40894,27 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>纵横四海·龙年世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>悉尼</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr">
         <is>
-          <t>国家体育场鸟巢</t>
+          <t>悉尼国际会议中心剧场</t>
         </is>
       </c>
       <c r="E1265" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="F1265" t="inlineStr">
         <is>
-          <t>1场·首站</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
@@ -40919,22 +40926,22 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>纵横四海·龙年世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>墨尔本</t>
         </is>
       </c>
       <c r="D1266" t="inlineStr">
         <is>
-          <t>福州海峡奥林匹克体育中心体育场</t>
+          <t>John Cain Arena</t>
         </is>
       </c>
       <c r="E1266" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="F1266" t="inlineStr">
@@ -40951,22 +40958,22 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>纵横四海·龙年世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>温州</t>
+          <t>奥克兰</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">
         <is>
-          <t>温州奥体中心主体育场</t>
+          <t>奥克兰Trusts体育馆</t>
         </is>
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F1267" t="inlineStr">
@@ -40983,27 +40990,27 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>纵横四海·龙年世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>清远</t>
         </is>
       </c>
       <c r="D1268" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场</t>
+          <t>清远体育中心体育场</t>
         </is>
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F1268" t="inlineStr">
         <is>
-          <t>1场·安可站</t>
+          <t>3场·跨年</t>
         </is>
       </c>
     </row>
@@ -41015,22 +41022,22 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>纵横四海·龙年世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>太原</t>
         </is>
       </c>
       <c r="D1269" t="inlineStr">
         <is>
-          <t>上海体育场</t>
+          <t>山西体育中心体育场</t>
         </is>
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="F1269" t="inlineStr">
@@ -41047,27 +41054,27 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>纵横四海·龙年世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
         <is>
-          <t>成都东安湖体育公园主体育场</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F1270" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -41079,22 +41086,22 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>纵横四海·龙年世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>南宁</t>
+          <t>哈尔滨</t>
         </is>
       </c>
       <c r="D1271" t="inlineStr">
         <is>
-          <t>广西体育中心体育场</t>
+          <t>哈尔滨国际会展体育中心体育场</t>
         </is>
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F1271" t="inlineStr">
@@ -41111,27 +41118,27 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>纵横四海·龙年世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南宁</t>
         </is>
       </c>
       <c r="D1272" t="inlineStr">
         <is>
-          <t>深圳大运中心体育场</t>
+          <t>广西体育中心体育场</t>
         </is>
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="F1272" t="inlineStr">
         <is>
-          <t>1场·收官</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -41143,27 +41150,27 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>天生李荣浩巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>贵阳</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
         <is>
-          <t>台北国际会议中心（TICC）</t>
+          <t>贵阳奥体中心体育场</t>
         </is>
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>2015-07-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="F1273" t="inlineStr">
         <is>
-          <t>1场·生日场</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
@@ -41175,27 +41182,27 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>有理想世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>呼和浩特</t>
         </is>
       </c>
       <c r="D1274" t="inlineStr">
         <is>
-          <t>乐视生态体育中心</t>
+          <t>呼和浩特体育场</t>
         </is>
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>2016-05-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="F1274" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
@@ -41207,27 +41214,27 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>有理想世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
         <is>
-          <t>梅赛德斯-奔驰文化中心</t>
+          <t>苏州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F1275" t="inlineStr">
         <is>
-          <t>1场</t>
+          <t>3场</t>
         </is>
       </c>
     </row>
@@ -41239,22 +41246,22 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>有理想世界巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>合肥</t>
+          <t>赣州</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
         <is>
-          <t>合肥体育中心体育馆</t>
+          <t>赣州市全民健身中心体育场</t>
         </is>
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>2016-07-30</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="F1276" t="inlineStr">
@@ -41266,283 +41273,283 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>香港</t>
+          <t>襄阳</t>
         </is>
       </c>
       <c r="D1277" t="inlineStr">
         <is>
-          <t>启德主场馆</t>
+          <t>襄阳奥林匹克体育中心</t>
         </is>
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="F1277" t="inlineStr">
         <is>
-          <t>4场·首站</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>大连</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场（大莲花）</t>
+          <t>大连体育中心体育场</t>
         </is>
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="F1278" t="inlineStr">
         <is>
-          <t>2场·内地首站</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>乌鲁木齐</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
         <is>
-          <t>广州大学城体育中心体育场</t>
+          <t>乌鲁木齐奥体中心体育场</t>
         </is>
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="F1279" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D1280" t="inlineStr">
         <is>
-          <t>重庆奥体中心体育场</t>
+          <t>成都东安湖体育公园主体育场</t>
         </is>
       </c>
       <c r="E1280" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F1280" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>2场·含9/6加场</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D1281" t="inlineStr">
         <is>
-          <t>苏州奥体中心体育场</t>
+          <t>上海体育场</t>
         </is>
       </c>
       <c r="E1281" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F1281" t="inlineStr">
         <is>
-          <t>3场·2025收官</t>
+          <t>2场</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>临沂</t>
         </is>
       </c>
       <c r="D1282" t="inlineStr">
         <is>
-          <t>深圳大运中心体育场</t>
+          <t>临沂奥体公园体育场</t>
         </is>
       </c>
       <c r="E1282" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F1282" t="inlineStr">
         <is>
-          <t>3场·2026首站</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D1283" t="inlineStr">
         <is>
-          <t>武汉体育中心主体育场</t>
+          <t>天津奥体中心体育场</t>
         </is>
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F1283" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>3场·原7/10-12因台风延期</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>衡阳</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
         <is>
-          <t>成都东安湖体育公园主体育场</t>
+          <t>衡阳市体育中心体育场</t>
         </is>
       </c>
       <c r="E1284" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F1284" t="inlineStr">
         <is>
-          <t>3场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>郑州</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
         <is>
-          <t>国家体育场（鸟巢）</t>
+          <t>郑州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1285" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F1285" t="inlineStr">
@@ -41554,91 +41561,91 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>黑马巡回演唱会</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="D1286" t="inlineStr">
         <is>
-          <t>南京奥体中心体育场</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E1286" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="F1286" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场·原10/17延期</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>年少有为世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="D1287" t="inlineStr">
         <is>
-          <t>西安奥体中心体育场</t>
+          <t>厦门嘉庚体育馆</t>
         </is>
       </c>
       <c r="E1287" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2019-03-30</t>
         </is>
       </c>
       <c r="F1287" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>年少有为世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>郑州</t>
+          <t>大连</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr">
         <is>
-          <t>郑州市奥林匹克中心体育场</t>
+          <t>大连体育中心体育馆</t>
         </is>
       </c>
       <c r="E1288" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2019-04-27</t>
         </is>
       </c>
       <c r="F1288" t="inlineStr">
@@ -41650,12 +41657,12 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>年少有为世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr">
@@ -41665,12 +41672,12 @@
       </c>
       <c r="D1289" t="inlineStr">
         <is>
-          <t>青岛市民健身中心体育场</t>
+          <t>青岛体育中心国信体育馆</t>
         </is>
       </c>
       <c r="E1289" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2019-05-11</t>
         </is>
       </c>
       <c r="F1289" t="inlineStr">
@@ -41682,187 +41689,187 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>年少有为世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1290" t="inlineStr">
         <is>
-          <t>沈阳</t>
+          <t>合肥</t>
         </is>
       </c>
       <c r="D1290" t="inlineStr">
         <is>
-          <t>沈阳奥林匹克体育中心体育场</t>
+          <t>合肥滨湖国际会展中心主展馆</t>
         </is>
       </c>
       <c r="E1290" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2019-07-27</t>
         </is>
       </c>
       <c r="F1290" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>年少有为世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1291" t="inlineStr">
         <is>
-          <t>太原</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D1291" t="inlineStr">
         <is>
-          <t>山西体育中心体育场</t>
+          <t>武汉体育中心体育馆</t>
         </is>
       </c>
       <c r="E1291" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2019-12-14</t>
         </is>
       </c>
       <c r="F1291" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>年少有为世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1292" t="inlineStr">
         <is>
-          <t>长沙</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D1292" t="inlineStr">
         <is>
-          <t>长沙贺龙体育场</t>
+          <t>重庆国际博览中心</t>
         </is>
       </c>
       <c r="E1292" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2019-12-21</t>
         </is>
       </c>
       <c r="F1292" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>麻雀巡回演唱会</t>
         </is>
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D1293" t="inlineStr">
         <is>
-          <t>重庆奥体中心体育场</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E1293" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2021-11-13</t>
         </is>
       </c>
       <c r="F1293" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>首站</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>纵横四海世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>南昌</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="D1294" t="inlineStr">
         <is>
-          <t>南昌国际体育中心体育场</t>
+          <t>南京奥体中心体育场</t>
         </is>
       </c>
       <c r="E1294" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="F1294" t="inlineStr">
         <is>
-          <t>2场</t>
+          <t>1场</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>纵横四海世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>温州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D1295" t="inlineStr">
         <is>
-          <t>温州奥体中心主体育场</t>
+          <t>杭州奥体中心体育场</t>
         </is>
       </c>
       <c r="E1295" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="F1295" t="inlineStr">
@@ -41874,59 +41881,59 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Evolution Nic Live进化巡回演唱会</t>
+          <t>纵横四海·龙年世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D1296" t="inlineStr">
         <is>
-          <t>杭州奥体中心体育场（大莲花）</t>
+          <t>国家体育场鸟巢</t>
         </is>
       </c>
       <c r="E1296" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="F1296" t="inlineStr">
         <is>
-          <t>2场·返场</t>
+          <t>1场·首站</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>谢霆锋</t>
+          <t>李荣浩</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Reborn Live巡回演唱会</t>
+          <t>纵横四海·龙年世界巡回演唱会</t>
         </is>
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="D1297" t="inlineStr">
         <is>
-          <t>北京首都体育馆</t>
+          <t>福州海峡奥林匹克体育中心体育场</t>
         </is>
       </c>
       <c r="E1297" t="inlineStr">
         <is>
-          <t>2003-10-25</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="F1297" t="inlineStr">
@@ -41938,30 +41945,1022 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>纵横四海·龙年世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>温州</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>温州奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>纵横四海·龙年世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>杭州奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>1场·安可站</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>纵横四海·龙年世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>上海体育场</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>纵横四海·龙年世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>成都东安湖体育公园主体育场</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>纵横四海·龙年世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>广西体育中心体育场</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>纵横四海·龙年世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>深圳大运中心体育场</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>1场·收官</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>天生李荣浩巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>台北国际会议中心（TICC）</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>2015-07-11</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>1场·生日场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>有理想世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>北京凯迪拉克中心</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>2016-05-20</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>有理想世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>上海梅赛德斯-奔驰文化中心</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>2016-07-09</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>李荣浩</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>有理想世界巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>合肥体育中心体育馆</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>2016-07-30</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
           <t>谢霆锋</t>
         </is>
       </c>
-      <c r="B1298" t="inlineStr">
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>香港启德主场馆</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>4场·首站</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>杭州奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>2场·内地首站</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>广州大学城体育中心体育场</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>3场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>重庆奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>苏州奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>3场·2025收官</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>深圳大运中心体育场</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>3场·2026首站</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>武汉体育中心主体育场</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>成都东安湖体育公园主体育场</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>3场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>国家体育场鸟巢</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>南京奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>西安奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>郑州奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>青岛市民健身中心体育场</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>沈阳奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>山西体育中心体育场</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>长沙贺龙体育场</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>重庆奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>南昌国际体育中心体育场</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>温州</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>温州奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Evolution Nic Live进化巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>杭州奥体中心体育场</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>2场·返场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Reborn Live巡回演唱会</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>北京首都体育馆</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>2003-10-25</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>谢霆锋</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
         <is>
           <t>Viva Live巡回演唱会</t>
         </is>
       </c>
-      <c r="C1298" t="inlineStr">
+      <c r="C1329" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="D1298" t="inlineStr">
+      <c r="D1329" t="inlineStr">
         <is>
           <t>红磡体育馆</t>
         </is>
       </c>
-      <c r="E1298" t="inlineStr">
+      <c r="E1329" t="inlineStr">
         <is>
           <t>2000-11-11</t>
         </is>
       </c>
-      <c r="F1298" t="inlineStr">
+      <c r="F1329" t="inlineStr">
         <is>
           <t>6场·首进红馆</t>
         </is>

--- a/歌手巡演专辑数据.xlsx
+++ b/歌手巡演专辑数据.xlsx
@@ -23180,7 +23180,11 @@
           <t>2023-09-09</t>
         </is>
       </c>
-      <c r="F710" t="inlineStr"/>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2场·9/10因病暂停退票</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -25640,7 +25644,11 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="F787" t="inlineStr"/>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -25668,7 +25676,11 @@
           <t>2024-06-15</t>
         </is>
       </c>
-      <c r="F788" t="inlineStr"/>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -25696,7 +25708,11 @@
           <t>2024-07-13</t>
         </is>
       </c>
-      <c r="F789" t="inlineStr"/>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -25724,7 +25740,11 @@
           <t>2024-07-27</t>
         </is>
       </c>
-      <c r="F790" t="inlineStr"/>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -25816,7 +25836,11 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="F793" t="inlineStr"/>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>1场</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -25940,7 +25964,11 @@
           <t>2024-11-23</t>
         </is>
       </c>
-      <c r="F797" t="inlineStr"/>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>2场</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
